--- a/KetQua_TaoPhieuNhapKho_Playwright.xlsx
+++ b/KetQua_TaoPhieuNhapKho_Playwright.xlsx
@@ -511,7 +511,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Công cụ: Playwright (Chromium)  |  Ngày thực hiện: 26/08/2026 02:16  |  Tổng Test Cases: 73  |  Pass: 73  |  Fail: 0  |  Thư mục ảnh: C:\xampp\htdocs\php-restaurant-main-main\testcase_receipt_screenshots</t>
+          <t>Công cụ: Playwright (Chromium)  |  Ngày thực hiện: 26/08/2026 02:25  |  Tổng Test Cases: 73  |  Pass: 73  |  Fail: 0  |  Thư mục ảnh: C:\xampp\htdocs\php-restaurant-main-main\testcase_receipt_screenshots</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L72" s="5" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L73" s="5" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L74" s="5" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L75" s="5" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:16</t>
+          <t>26/08/2026 02:25</t>
         </is>
       </c>
       <c r="L76" s="5" t="inlineStr">

--- a/KetQua_TaoPhieuNhapKho_Playwright.xlsx
+++ b/KetQua_TaoPhieuNhapKho_Playwright.xlsx
@@ -511,7 +511,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Công cụ: Playwright (Chromium)  |  Ngày thực hiện: 26/08/2026 02:25  |  Tổng Test Cases: 73  |  Pass: 73  |  Fail: 0  |  Thư mục ảnh: C:\xampp\htdocs\php-restaurant-main-main\testcase_receipt_screenshots</t>
+          <t>Công cụ: Playwright (Chromium)  |  Ngày thực hiện: 26/08/2026 02:49  |  Tổng Test Cases: 73  |  Pass: 73  |  Fail: 0  |  Thư mục ảnh: C:\xampp\htdocs\php-restaurant-main-main\testcase_receipt_screenshots</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -686,12 +686,12 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>001_TC01_UI_man_hinh_tao_phieu.png</t>
+          <t>002_TC02_UI_thong_tin_chung.png</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>001_TC01_UI_man_hinh_tao_phieu.png</t>
+          <t>003_TC03_UI_ngay_nhap_mac_dinh.png</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>002_TC04_bang_chi_tiet_nguyen_lieu.png</t>
+          <t>004_TC04_bang_chi_tiet_nguyen_lieu.png</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>002_TC04_bang_chi_tiet_nguyen_lieu.png</t>
+          <t>005_TC05_dropdown_nguyen_lieu.png</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>002_TC04_bang_chi_tiet_nguyen_lieu.png</t>
+          <t>006_TC06_tong_cong_mac_dinh.png</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>002_TC04_bang_chi_tiet_nguyen_lieu.png</t>
+          <t>007_TC07_cac_nut_chuc_nang.png</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>003_TC08_nut_quay_lai.png</t>
+          <t>008_TC08_nut_quay_lai.png</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>004_TC09_admin_truy_cap.png</t>
+          <t>009_TC09_admin_truy_cap.png</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>005_TC10_manager_truy_cap.png</t>
+          <t>010_TC10_manager_truy_cap.png</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>006_TC11_staff_bi_chan.png</t>
+          <t>011_TC11_staff_bi_chan.png</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>007_TC12_cashier_bi_chan.png</t>
+          <t>012_TC12_cashier_bi_chan.png</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1355,12 +1355,12 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>008_TC13_guest_redirect_login.png</t>
+          <t>013_TC13_guest_redirect_login.png</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>009_TC14_staff_post_api_blocked.png</t>
+          <t>014_TC14_staff_post_api_blocked.png</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>008_TC13_guest_redirect_login.png</t>
+          <t>015_TC15_guest_api_blocked.png</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>010_TC16_supplier_empty.png</t>
+          <t>016_TC16_supplier_empty.png</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>011_TC17_supplier_valid.png</t>
+          <t>017_TC17_supplier_valid.png</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>012_TC18_supplier_all_spaces.png</t>
+          <t>018_TC18_supplier_all_spaces.png</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -1720,12 +1720,12 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>013_TC19_supplier_1_char.png</t>
+          <t>019_TC19_supplier_1_char.png</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>014_TC20_supplier_100_chars.png</t>
+          <t>020_TC20_supplier_100_chars.png</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>015_TC21_supplier_over_100_chars.png</t>
+          <t>021_TC21_supplier_over_100_chars.png</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>016_TC22_supplier_special_chars.png</t>
+          <t>022_TC22_supplier_special_chars.png</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>017_TC23_receipt_date_empty.png</t>
+          <t>023_TC23_receipt_date_empty.png</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>018_TC24_receipt_date_today.png</t>
+          <t>024_TC24_receipt_date_today.png</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>019_TC25_receipt_date_past.png</t>
+          <t>025_TC25_receipt_date_past.png</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>020_TC26_receipt_date_future.png</t>
+          <t>026_TC26_receipt_date_future.png</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>021_TC27_receipt_date_too_old.png</t>
+          <t>027_TC27_receipt_date_too_old.png</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>021_TC27_receipt_date_too_old.png</t>
+          <t>028_TC28_invalid_date_format_api.png</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>021_TC27_receipt_date_too_old.png</t>
+          <t>029_TC29_leap_year_test.png</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>022_TC30_note_empty.png</t>
+          <t>030_TC30_note_empty.png</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>023_TC31_note_valid.png</t>
+          <t>031_TC31_note_valid.png</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -2512,12 +2512,12 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>024_TC32_note_500_chars.png</t>
+          <t>032_TC32_note_500_chars.png</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>025_TC33_note_over_500_chars.png</t>
+          <t>033_TC33_note_over_500_chars.png</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>026_TC34_note_multiline.png</t>
+          <t>034_TC34_note_multiline.png</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>027_TC35_ingredient_empty_select.png</t>
+          <t>035_TC35_ingredient_empty_select.png</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>028_TC36_ingredient_valid_selected.png</t>
+          <t>036_TC36_ingredient_valid_selected.png</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>028_TC36_ingredient_valid_selected.png</t>
+          <t>037_TC37_invalid_ingredient_id_api.png</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>029_TC38_duplicate_ingredient_rows.png</t>
+          <t>038_TC38_duplicate_ingredient_rows.png</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>030_TC39_auto_fill_price.png</t>
+          <t>039_TC39_auto_fill_price.png</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>031_TC40_change_ingredient_updates_price.png</t>
+          <t>040_TC40_change_ingredient_updates_price.png</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>032_TC41_qty_empty.png</t>
+          <t>041_TC41_qty_empty.png</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>033_TC42_qty_zero.png</t>
+          <t>042_TC42_qty_zero.png</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>034_TC43_qty_negative.png</t>
+          <t>043_TC43_qty_negative.png</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>035_TC44_qty_valid_int.png</t>
+          <t>044_TC44_qty_valid_int.png</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>036_TC45_qty_valid_decimal.png</t>
+          <t>045_TC45_qty_valid_decimal.png</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>037_TC46_qty_3_decimals.png</t>
+          <t>046_TC46_qty_3_decimals.png</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>038_TC47_qty_over_3_decimals.png</t>
+          <t>047_TC47_qty_over_3_decimals.png</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>039_TC48_qty_over_max.png</t>
+          <t>048_TC48_qty_over_max.png</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>040_TC49_price_empty.png</t>
+          <t>049_TC49_price_empty.png</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>041_TC50_price_negative.png</t>
+          <t>050_TC50_price_negative.png</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -3671,12 +3671,12 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>042_TC51_price_zero.png</t>
+          <t>051_TC51_price_zero.png</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>043_TC52_price_valid_positive.png</t>
+          <t>052_TC52_price_valid_positive.png</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>044_TC53_price_decimal.png</t>
+          <t>053_TC53_price_decimal.png</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>045_TC54_price_over_max.png</t>
+          <t>054_TC54_price_over_max.png</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>046_TC55_price_custom_edit.png</t>
+          <t>055_TC55_price_custom_edit.png</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>047_TC56_add_row_click.png</t>
+          <t>056_TC56_add_row_click.png</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>048_TC57_remove_row_click.png</t>
+          <t>057_TC57_remove_row_click.png</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
@@ -4098,12 +4098,12 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>049_TC58_add_5_rows.png</t>
+          <t>058_TC58_add_5_rows.png</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>050_TC59_calc_subtotal_on_qty.png</t>
+          <t>059_TC59_calc_subtotal_on_qty.png</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>051_TC60_calc_subtotal_on_price.png</t>
+          <t>060_TC60_calc_subtotal_on_price.png</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>052_TC61_calc_grand_total.png</t>
+          <t>061_TC61_calc_grand_total.png</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>053_TC62_currency_format.png</t>
+          <t>062_TC62_currency_format.png</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>054_TC63_submit_zero_rows.png</t>
+          <t>063_TC63_submit_zero_rows.png</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
@@ -4463,13 +4463,13 @@
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>055_TC64_submit_valid_single_row.png
-056_TC64_after_submit_success.png</t>
+          <t>064_TC64_submit_valid_single_row.png
+065_TC64_after_submit_success.png</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>057_TC65_submit_3_valid_rows.png</t>
+          <t>066_TC65_submit_3_valid_rows.png</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
@@ -4588,12 +4588,12 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>058_TC66_old_input_retained.png</t>
+          <t>067_TC66_old_input_retained.png</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
@@ -4650,13 +4650,13 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>059_TC67_multiple_detailed_errors.png
-060_TC67_error_box_displayed.png</t>
+          <t>068_TC67_multiple_detailed_errors.png
+069_TC67_error_box_displayed.png</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>061_TC68_double_click_protection.png</t>
+          <t>070_TC68_double_click_protection.png</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>062_TC69_quick_restock_params.png</t>
+          <t>071_TC69_quick_restock_params.png</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L72" s="5" t="inlineStr">
@@ -4835,12 +4835,12 @@
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>063_TC70_create_from_restock_cart.png</t>
+          <t>072_TC70_create_from_restock_cart.png</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L73" s="5" t="inlineStr">
@@ -4896,13 +4896,13 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>064_TC71_xss_injection_test.png
-065_TC71_after_xss_submit.png</t>
+          <t>073_TC71_xss_injection_test.png
+074_TC71_after_xss_submit.png</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L74" s="5" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>066_TC72_sqli_injection_test.png</t>
+          <t>075_TC72_sqli_injection_test.png</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L75" s="5" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>067_TC73_db_data_integrity.png</t>
+          <t>076_TC73_db_data_integrity.png</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026 02:25</t>
+          <t>26/08/2026 02:49</t>
         </is>
       </c>
       <c r="L76" s="5" t="inlineStr">
